--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250606103858</t>
+    <t>20250616134740</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06T10:38:58+01:00</t>
+    <t>2025-06-16T13:47:40+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134740</t>
+    <t>20250624152101</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:40+01:00</t>
+    <t>2025-06-24T15:21:01+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250624152101</t>
+    <t>20251028115835</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T15:21:01+01:00</t>
+    <t>2025-10-28T11:58:35+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,13 +102,13 @@
     <t>57171008</t>
   </si>
   <si>
-    <t>structure du système hématopoïétique</t>
-  </si>
-  <si>
-    <t>1290040004</t>
-  </si>
-  <si>
-    <t>œil entier</t>
+    <t>système hématopoïétique</t>
+  </si>
+  <si>
+    <t>81745001</t>
+  </si>
+  <si>
+    <t>œil</t>
   </si>
   <si>
     <t>272673000</t>
@@ -174,7 +174,7 @@
     <t>119253004</t>
   </si>
   <si>
-    <t>voie aérodigestive supérieure</t>
+    <t>voies aérodigestives supérieures</t>
   </si>
   <si>
     <t/>

--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251028115835</t>
+    <t>20251216141840</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T11:58:35+01:00</t>
+    <t>2025-12-16T14:18:40+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141840</t>
+    <t>20260220142105</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:40+01:00</t>
+    <t>2026-02-20T14:21:05+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142105</t>
+    <t>20260311144904</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:05+01:00</t>
+    <t>2026-03-11T14:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144904</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:04+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-rcp-appareil-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150251</t>
+    <t>20260619134043</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:51+01:00</t>
+    <t>2026-06-19T13:40:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,12 +93,6 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>387910009</t>
-  </si>
-  <si>
-    <t>glande endocrine</t>
-  </si>
-  <si>
     <t>57171008</t>
   </si>
   <si>
@@ -108,7 +102,7 @@
     <t>81745001</t>
   </si>
   <si>
-    <t>œil</t>
+    <t>œil proprement dit</t>
   </si>
   <si>
     <t>272673000</t>
@@ -132,7 +126,7 @@
     <t>86762007</t>
   </si>
   <si>
-    <t>système digestif</t>
+    <t>appareil digestif</t>
   </si>
   <si>
     <t>53065001</t>
@@ -156,13 +150,7 @@
     <t>122489005</t>
   </si>
   <si>
-    <t>système urinaire</t>
-  </si>
-  <si>
-    <t>312419003</t>
-  </si>
-  <si>
-    <t>appareil respiratoire et/ou cavité thoracique</t>
+    <t>appareil urinaire</t>
   </si>
   <si>
     <t>87784001</t>
@@ -175,6 +163,18 @@
   </si>
   <si>
     <t>voies aérodigestives supérieures</t>
+  </si>
+  <si>
+    <t>699593001</t>
+  </si>
+  <si>
+    <t>cavité thoracique et/ou contenu intrathoracique</t>
+  </si>
+  <si>
+    <t>113331007</t>
+  </si>
+  <si>
+    <t>système endocrinien</t>
   </si>
   <si>
     <t/>
